--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:38</t>
+    <t xml:space="preserve">2026-09-09 22:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:24</t>
+    <t xml:space="preserve">2026-09-12 19:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_arica y parinacota.xlsx
@@ -36,12 +36,12 @@
     <t xml:space="preserve">Arica y Parinacota</t>
   </si>
   <si>
+    <t xml:space="preserve">General Lagos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Camarones</t>
   </si>
   <si>
-    <t xml:space="preserve">General Lagos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Putre</t>
   </si>
   <si>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:41</t>
+    <t xml:space="preserve">2026-09-24 00:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -487,13 +487,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>15102</v>
+        <v>15202</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>100.94</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="3">
@@ -504,13 +504,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>15202</v>
+        <v>15102</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>87.38</v>
+        <v>34.83</v>
       </c>
     </row>
     <row r="4">
@@ -527,7 +527,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>77.85</v>
+        <v>25.95</v>
       </c>
     </row>
     <row r="5">
@@ -544,7 +544,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>17.1</v>
+        <v>6.91</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:18</t>
+    <t xml:space="preserve">2026-09-27 22:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:08</t>
+    <t xml:space="preserve">2026-09-29 11:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,7 +493,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>45.62</v>
+        <v>456.19</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>34.83</v>
+        <v>348.31</v>
       </c>
     </row>
     <row r="4">
@@ -527,7 +527,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>25.95</v>
+        <v>259.54</v>
       </c>
     </row>
     <row r="5">
@@ -544,7 +544,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6.91</v>
+        <v>69.06</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:02</t>
+    <t xml:space="preserve">2026-10-01 19:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:27</t>
+    <t xml:space="preserve">2026-10-02 13:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:15</t>
+    <t xml:space="preserve">2026-10-05 07:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
